--- a/duoki_editor/resources/data/blank/动物园-一般疑问句_否定答句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/动物园-一般疑问句_否定答句认读-1-blank.xlsx
@@ -61,10 +61,10 @@
     <t>一般疑问句_认读_1_问_2</t>
   </si>
   <si>
-    <t>一般疑问句_认读_1_问_3</t>
-  </si>
-  <si>
-    <t>一般疑问句_认读_1_答</t>
+    <t>(一般疑问句_认读_1_问_答案)</t>
+  </si>
+  <si>
+    <t>一般疑问句_认读_1_帮助</t>
   </si>
   <si>
     <t>结束语_1</t>
@@ -106,13 +106,13 @@
     <t>`我来帮你吧！{sentence_answer_en_2}`</t>
   </si>
   <si>
-    <t>Fantastic！{user_name}，我把所有的宝石都给你们，一共是20颗！我要去找宝石精灵拿宝石了，下次我会带更多的宝石来！Bye！</t>
-  </si>
-  <si>
-    <t>{user_name}，这次{npc2_name}帮了你，只能得到10颗宝石哦！我还有很多很多闪亮的宝石，你们下次再来挑战吧！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>Fantastic！{user_name}，我把所有的宝石都给你们，一共是10颗！我要去找宝石精灵拿宝石了，下次我会带更多的宝石来！Bye！</t>
+  </si>
+  <si>
+    <t>{user_name}，这次{npc2_name}帮了你，只能得到5颗宝石哦！我还有很多很多闪亮的宝石，你们下次再来挑战吧！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
